--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488245_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488245_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1713</v>
+        <v>12.5861</v>
       </c>
       <c r="E2" t="n">
-        <v>11.8136</v>
+        <v>12.8591</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6423</v>
+        <v>-0.273</v>
       </c>
       <c r="G2" t="n">
         <v>9.8931</v>
@@ -610,13 +610,13 @@
         <v>2.594</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2674</v>
+        <v>1.1475</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1256</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1418</v>
+        <v>0.2275</v>
       </c>
       <c r="V2" t="n">
         <v>0.06320000000000001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2934</v>
+        <v>5.991</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7935</v>
+        <v>5.3925</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4999</v>
+        <v>0.5984</v>
       </c>
       <c r="G3" t="n">
         <v>4.1442</v>
@@ -688,13 +688,13 @@
         <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1415</v>
+        <v>0.8391</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0709</v>
+        <v>0.5282</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2124</v>
+        <v>0.3109</v>
       </c>
       <c r="V3" t="n">
         <v>1.0076</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6665</v>
+        <v>2.9559</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9563</v>
+        <v>3.3688</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2898</v>
+        <v>-0.4129</v>
       </c>
       <c r="G4" t="n">
         <v>1.3702</v>
@@ -766,13 +766,13 @@
         <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1814</v>
+        <v>0.4707</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0533</v>
+        <v>0.4657</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1281</v>
+        <v>0.005</v>
       </c>
       <c r="V4" t="n">
         <v>0.1886</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7902</v>
+        <v>2.4322</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3745</v>
+        <v>2.9903</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4157</v>
+        <v>-0.5581</v>
       </c>
       <c r="G5" t="n">
-        <v>2.546</v>
+        <v>2.704</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1801</v>
+        <v>1.5337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3658</v>
+        <v>1.1702</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5631</v>
+        <v>3.5211</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1898</v>
+        <v>2.6276</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3732</v>
+        <v>0.8935</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0171</v>
+        <v>-0.8171</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0097</v>
+        <v>-1.0938</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0074</v>
+        <v>0.2767</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.7793</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.8175</v>
+        <v>-2.0382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7227</v>
+        <v>1.6138</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6289</v>
+        <v>1.1935</v>
       </c>
       <c r="U5" t="n">
-        <v>2.0938</v>
+        <v>0.4203</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6992</v>
+        <v>-1.7003</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3139</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6992</v>
+        <v>-2.0142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1897</v>
+        <v>0.8928</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9448</v>
+        <v>0.3635</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7551</v>
+        <v>0.5293</v>
       </c>
       <c r="G6" t="n">
-        <v>2.704</v>
+        <v>2.546</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5337</v>
+        <v>2.1801</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1702</v>
+        <v>0.3658</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5211</v>
+        <v>3.5631</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6276</v>
+        <v>3.1898</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8935</v>
+        <v>0.3732</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8171</v>
+        <v>-1.0171</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0938</v>
+        <v>-1.0097</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2767</v>
+        <v>-0.0074</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1853</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0382</v>
+        <v>-4.8175</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3713</v>
+        <v>2.8253</v>
       </c>
       <c r="T6" t="n">
-        <v>0.148</v>
+        <v>1.6179</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2233</v>
+        <v>1.2074</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7003</v>
+        <v>-1.6992</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3139</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.0142</v>
+        <v>-1.6992</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>J. PINILLA NUÑEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7459</v>
+        <v>0.6221</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7255</v>
+        <v>0.6221</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0204</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2556</v>
+        <v>0.6221</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4277</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.172</v>
+        <v>0.6221</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1274</v>
+        <v>0.6221</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0859</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0415</v>
+        <v>0.6221</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5135999999999999</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.631</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5981</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0328</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PINILLA NUÑEZ</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6221</v>
+        <v>0.5014</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6221</v>
+        <v>0.4317</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.0697</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6221</v>
+        <v>-0.2556</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.4277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6221</v>
+        <v>0.172</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6221</v>
+        <v>0.1274</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.0859</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6221</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.383</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.1306</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.3864</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.3044</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>J. MALPICA PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.279</v>
+        <v>0.1716</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9253</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6464</v>
+        <v>0.1716</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6845</v>
+        <v>0.1306</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7106</v>
+        <v>0.1306</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0261</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8933</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8044</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9111</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2088</v>
+        <v>0.1306</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0938</v>
+        <v>0.1306</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.115</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9646</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2234</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9797</v>
+        <v>0.041</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9972</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0174</v>
+        <v>0.041</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.6441</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.6436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MALPICA PEREZ</t>
+          <t>D. LEMOINE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.147</v>
+        <v>-0.2005</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1.0717</v>
       </c>
       <c r="F10" t="n">
-        <v>0.147</v>
+        <v>-1.2722</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1306</v>
+        <v>2.1871</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1306</v>
+        <v>0.6296</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.5574</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2.0009</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.5281</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4729</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1306</v>
+        <v>0.1862</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1306</v>
+        <v>0.1016</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0164</v>
+        <v>0.1999</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-0.0028</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0164</v>
+        <v>0.2027</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.958</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.958</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. LEMOINE</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8187</v>
+        <v>-0.3447</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5273</v>
+        <v>1.0555</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.346</v>
+        <v>-1.4002</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1871</v>
+        <v>1.6845</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6296</v>
+        <v>2.7106</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5574</v>
+        <v>-1.0261</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0009</v>
+        <v>2.8933</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5281</v>
+        <v>3.8044</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4729</v>
+        <v>-0.9111</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1862</v>
+        <v>-1.2088</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1016</v>
+        <v>-1.0938</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.115</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3706</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-2.9646</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>2.2234</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4183</v>
+        <v>1.3561</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5471</v>
+        <v>1.1273</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1288</v>
+        <v>0.2288</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.958</v>
+        <v>-2.6441</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.958</v>
+        <v>-2.6436</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4743</v>
+        <v>-6.1751</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5907</v>
+        <v>-5.2421</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8837</v>
+        <v>-0.9329</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7962</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6325</v>
+        <v>0.9317</v>
       </c>
       <c r="T12" t="n">
-        <v>0.051</v>
+        <v>0.3995</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5815</v>
+        <v>0.5322</v>
       </c>
       <c r="V12" t="n">
         <v>-2.0136</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.6121</v>
+        <v>19.4328</v>
       </c>
       <c r="E13" t="n">
-        <v>22.0922</v>
+        <v>22.9131</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.480300000000001</v>
+        <v>-3.4803</v>
       </c>
       <c r="G13" t="n">
         <v>21.23</v>
@@ -1453,10 +1453,10 @@
         <v>-8.0303</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.646199999999999</v>
+        <v>-8.6462</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6158999999999999</v>
+        <v>0.6159</v>
       </c>
       <c r="P13" t="n">
         <v>-1.8528</v>
@@ -1468,10 +1468,10 @@
         <v>14.823</v>
       </c>
       <c r="S13" t="n">
-        <v>8.990800000000002</v>
+        <v>9.811499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>5.7329</v>
+        <v>6.5536</v>
       </c>
       <c r="U13" t="n">
         <v>3.2579</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0284</v>
+        <v>0.801</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4097</v>
+        <v>3.7242</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3813</v>
+        <v>-2.9232</v>
       </c>
       <c r="G14" t="n">
         <v>0.2957</v>
@@ -1546,13 +1546,13 @@
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0264</v>
+        <v>-1.2538</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4813</v>
+        <v>-0.2042</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5077</v>
+        <v>-1.0496</v>
       </c>
       <c r="V14" t="n">
         <v>1.5738</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. LÓPEZ CALZADA</t>
+          <t>D. LARA CALDERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3221</v>
+        <v>0.6821</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3221</v>
+        <v>4.298</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-3.6158</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3221</v>
+        <v>-3.4055</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3221</v>
+        <v>-3.0478</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-0.3577</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3221</v>
+        <v>2.0783</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3221</v>
+        <v>-1.2809</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.3592</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-5.4838</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-1.767</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-3.7168</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.9646</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-1.4655</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.6833</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0.7822</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.2943</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>6.6087</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="16">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. LARA CALDERA</t>
+          <t>L. LÓPEZ CALZADA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2743</v>
+        <v>0.3221</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1021</v>
+        <v>0.3221</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.8277</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.4055</v>
+        <v>0.3221</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.0478</v>
+        <v>0.3221</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3577</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0783</v>
+        <v>0.3221</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2809</v>
+        <v>0.3221</v>
       </c>
       <c r="L18" t="n">
-        <v>3.3592</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.4838</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.767</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.7168</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9646</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8733</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8792</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9941</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6.2943</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>6.6087</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5697</v>
+        <v>-1.1337</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4295</v>
+        <v>-0.8212</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1402</v>
+        <v>-0.3125</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9348</v>
@@ -1936,13 +1936,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7357</v>
+        <v>0.1716</v>
       </c>
       <c r="T19" t="n">
-        <v>0.434</v>
+        <v>0.0423</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3017</v>
+        <v>0.1293</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>J. VALVERDE PIZARRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5857</v>
+        <v>-1.6218</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2529</v>
+        <v>1.1135</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8387</v>
+        <v>-2.7353</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.5478</v>
+        <v>0.0781</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1608</v>
+        <v>0.6279</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.3871</v>
+        <v>-0.5498</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3782</v>
+        <v>1.1365</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0085</v>
+        <v>1.095</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6303</v>
+        <v>0.0415</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.9261</v>
+        <v>-1.0584</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1693</v>
+        <v>-0.4671</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.7568</v>
+        <v>-0.5913</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.2234</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.6322</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4087</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2199</v>
+        <v>-0.3675</v>
       </c>
       <c r="T20" t="n">
-        <v>0.102</v>
+        <v>-0.023</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3219</v>
+        <v>-0.3445</v>
       </c>
       <c r="V20" t="n">
-        <v>4.4054</v>
+        <v>-1.8883</v>
       </c>
       <c r="W20" t="n">
-        <v>4.4049</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0005</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VALVERDE PIZARRO</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8915</v>
+        <v>-1.8095</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9176</v>
+        <v>-0.7743</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8092</v>
+        <v>-1.0352</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0781</v>
+        <v>-2.7624</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6279</v>
+        <v>-0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5498</v>
+        <v>-1.8124</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1365</v>
+        <v>-0.5757</v>
       </c>
       <c r="K21" t="n">
-        <v>1.095</v>
+        <v>0.0772</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0415</v>
+        <v>-0.6529</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0584</v>
+        <v>-2.1867</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4671</v>
+        <v>-1.0271</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5913</v>
+        <v>-1.1596</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6372</v>
+        <v>-0.3441</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2189</v>
+        <v>-0.1986</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4183</v>
+        <v>-0.1455</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8883</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3816</v>
+        <v>-2.1841</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0681</v>
+        <v>-0.1388</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3135</v>
+        <v>-2.0453</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7624</v>
+        <v>-3.5478</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.95</v>
+        <v>-0.1608</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8124</v>
+        <v>-3.3871</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5757</v>
+        <v>0.3782</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0772</v>
+        <v>1.0085</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6529</v>
+        <v>-0.6303</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1867</v>
+        <v>-3.9261</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0271</v>
+        <v>-1.1693</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1596</v>
+        <v>-2.7568</v>
       </c>
       <c r="P22" t="n">
-        <v>1.297</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R22" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9162</v>
+        <v>-0.8183</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4924</v>
+        <v>-0.2897</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4238</v>
+        <v>-0.5285</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.4054</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>4.4049</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4823</v>
+        <v>-2.4245</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8752</v>
+        <v>-1.071</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6072</v>
+        <v>-1.3535</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6273</v>
@@ -2248,13 +2248,13 @@
         <v>2.4087</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3368</v>
+        <v>-1.279</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4961</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8406</v>
+        <v>-0.587</v>
       </c>
       <c r="V23" t="n">
         <v>-0.0005</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4766</v>
+        <v>-3.8318</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5731</v>
+        <v>-1.0834</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9036</v>
+        <v>-2.7484</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6963</v>
@@ -2326,13 +2326,13 @@
         <v>1.4823</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2806</v>
+        <v>-0.6358</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9302</v>
+        <v>-0.4405</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3504</v>
+        <v>-0.1952</v>
       </c>
       <c r="V24" t="n">
         <v>0.9444</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4935</v>
+        <v>-6.7502</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2225</v>
+        <v>-2.7328</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.271</v>
+        <v>-4.0173</v>
       </c>
       <c r="G25" t="n">
         <v>-4.5958</v>
@@ -2404,13 +2404,13 @@
         <v>2.0382</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4361</v>
+        <v>-1.6928</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2584</v>
+        <v>-0.7688</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1776</v>
+        <v>-0.924</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5733</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.6119</v>
+        <v>-17.3062</v>
       </c>
       <c r="E26" t="n">
-        <v>3.4802</v>
+        <v>3.480499999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-22.0924</v>
+        <v>-20.7865</v>
       </c>
       <c r="G26" t="n">
         <v>-21.2298</v>
@@ -2458,10 +2458,10 @@
         <v>8.0304</v>
       </c>
       <c r="K26" t="n">
-        <v>8.646399999999998</v>
+        <v>8.6464</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6159</v>
+        <v>-0.6159000000000004</v>
       </c>
       <c r="M26" t="n">
         <v>-29.2603</v>
@@ -2482,22 +2482,22 @@
         <v>16.6759</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.9908</v>
+        <v>-7.6852</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.2579</v>
+        <v>-3.2578</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.732699999999999</v>
+        <v>-4.4272</v>
       </c>
       <c r="V26" t="n">
-        <v>9.755799999999999</v>
+        <v>9.755800000000001</v>
       </c>
       <c r="W26" t="n">
         <v>13.5309</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.774900000000001</v>
+        <v>-3.7749</v>
       </c>
     </row>
   </sheetData>
